--- a/resources/templates/standard/L1200-03.xlsx
+++ b/resources/templates/standard/L1200-03.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>지그 관리대장</t>
   </si>
@@ -628,10 +631,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -640,7 +645,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1" s="4"/>
     </row>
@@ -655,7 +660,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" s="4"/>
     </row>
@@ -670,43 +675,43 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" s="6"/>
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -714,22 +719,22 @@
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="10"/>
